--- a/r/case2/outputs/results/CaseStudy_2_results.xlsx
+++ b/r/case2/outputs/results/CaseStudy_2_results.xlsx
@@ -32,10 +32,10 @@
     <t xml:space="preserve">age</t>
   </si>
   <si>
-    <t xml:space="preserve">65.38 ± 8.27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[45.00, 86.00]</t>
+    <t xml:space="preserve">65.30 ± 6.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[49.00, 82.00]</t>
   </si>
   <si>
     <t xml:space="preserve">sex</t>
@@ -50,19 +50,19 @@
     <t xml:space="preserve">criq</t>
   </si>
   <si>
-    <t xml:space="preserve">96.02 ± 11.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[73.50, 120.10]</t>
+    <t xml:space="preserve">96.10 ± 11.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[74.00, 119.00]</t>
   </si>
   <si>
     <t xml:space="preserve">moca</t>
   </si>
   <si>
-    <t xml:space="preserve">21.63 ± 6.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[8.17, 30.00]</t>
+    <t xml:space="preserve">21.73 ± 6.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[8.00, 30.00]</t>
   </si>
   <si>
     <t xml:space="preserve">Analysis</t>
@@ -581,22 +581,22 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-4620.50621534643</v>
+        <v>-4059.66754157029</v>
       </c>
       <c r="D2" t="n">
-        <v>1954</v>
+        <v>1719</v>
       </c>
       <c r="E2" t="n">
-        <v>15.869140625</v>
+        <v>16.11328125</v>
       </c>
       <c r="F2" t="n">
-        <v>39.794921875</v>
+        <v>39.55078125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.859705101358567</v>
+        <v>0.862051290640671</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1805</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="3">
@@ -607,22 +607,22 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>-3512.15396929978</v>
+        <v>-3343.0644034786</v>
       </c>
       <c r="D3" t="n">
-        <v>1514</v>
+        <v>1442</v>
       </c>
       <c r="E3" t="n">
         <v>1.220703125</v>
       </c>
       <c r="F3" t="n">
-        <v>15.380859375</v>
+        <v>14.16015625</v>
       </c>
       <c r="G3" t="n">
-        <v>0.886844588903315</v>
+        <v>0.88418203106963</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2155</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="4">
@@ -633,10 +633,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>-20.9113096132462</v>
+        <v>-18.611234396768</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>14.6484375</v>
@@ -648,7 +648,7 @@
         <v>0.97884285789975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7685</v>
+        <v>0.7935</v>
       </c>
     </row>
     <row r="5">
@@ -659,22 +659,22 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>-15.1935836598486</v>
+        <v>-12.8419509115664</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>28.076171875</v>
+        <v>33.935546875</v>
       </c>
       <c r="F5" t="n">
-        <v>29.541015625</v>
+        <v>34.423828125</v>
       </c>
       <c r="G5" t="n">
-        <v>0.969306831498649</v>
+        <v>0.570617428748999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.793</v>
+        <v>0.8215</v>
       </c>
     </row>
     <row r="6">
@@ -685,22 +685,22 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>-10.5445090885832</v>
+        <v>-8.62436401288717</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>19.287109375</v>
+        <v>28.076171875</v>
       </c>
       <c r="F6" t="n">
-        <v>19.775390625</v>
+        <v>28.80859375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.871154050695262</v>
+        <v>0.969306831498649</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8215</v>
+        <v>0.8415</v>
       </c>
     </row>
     <row r="7">
@@ -711,10 +711,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>-2457.61840751944</v>
+        <v>-2432.35014499723</v>
       </c>
       <c r="D7" t="n">
-        <v>1048</v>
+        <v>1038</v>
       </c>
       <c r="E7" t="n">
         <v>1.220703125</v>
@@ -723,10 +723,10 @@
         <v>7.8125</v>
       </c>
       <c r="G7" t="n">
-        <v>0.911068835052885</v>
+        <v>0.908603002071589</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0395</v>
+        <v>0.041</v>
       </c>
     </row>
   </sheetData>
@@ -762,16 +762,16 @@
         <v>31</v>
       </c>
       <c r="B2" t="n">
-        <v>29.7835802750166</v>
+        <v>31.669769868757</v>
       </c>
       <c r="C2" t="n">
-        <v>15.1569640536638</v>
+        <v>14.6684309495277</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0571662777858673</v>
+        <v>0.0375874561216122</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -779,13 +779,13 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.316378108326919</v>
+        <v>-0.332966490792945</v>
       </c>
       <c r="C3" t="n">
-        <v>0.571788907220557</v>
+        <v>0.571029032845666</v>
       </c>
       <c r="D3" t="n">
-        <v>0.583469479592635</v>
+        <v>0.563461827283014</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -796,13 +796,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.178927089426051</v>
+        <v>-0.200659461890056</v>
       </c>
       <c r="C4" t="n">
-        <v>0.118330932500306</v>
+        <v>0.146126536878362</v>
       </c>
       <c r="D4" t="n">
-        <v>0.139240531119051</v>
+        <v>0.178186278495677</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -813,13 +813,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0775644099685022</v>
+        <v>0.0755869199868573</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0898228427730331</v>
+        <v>0.0895276682326294</v>
       </c>
       <c r="D5" t="n">
-        <v>0.393564979243042</v>
+        <v>0.404085656410112</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -873,16 +873,16 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>-494.290572773122</v>
+        <v>-544.682350651251</v>
       </c>
       <c r="E2" t="n">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0815</v>
+        <v>0.0755</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4075</v>
+        <v>0.3775</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>-1963.32783474632</v>
+        <v>-1887.66779434598</v>
       </c>
       <c r="E3" t="n">
-        <v>827</v>
+        <v>796</v>
       </c>
       <c r="F3" t="n">
         <v>0.029</v>
@@ -925,16 +925,16 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>-897.286564953598</v>
+        <v>-761.193300977685</v>
       </c>
       <c r="E4" t="n">
-        <v>393</v>
+        <v>335</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0815</v>
+        <v>0.092</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4075</v>
+        <v>0.46</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
@@ -951,16 +951,16 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>-3378.16114194639</v>
+        <v>-3002.99465767282</v>
       </c>
       <c r="E5" t="n">
-        <v>1421</v>
+        <v>1263</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0715</v>
+        <v>0.0805</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3575</v>
+        <v>0.4025</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
@@ -977,16 +977,16 @@
         <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>-1043.98507177305</v>
+        <v>-877.702938593218</v>
       </c>
       <c r="E6" t="n">
-        <v>444</v>
+        <v>376</v>
       </c>
       <c r="F6" t="n">
-        <v>0.125</v>
+        <v>0.14</v>
       </c>
       <c r="G6" t="n">
-        <v>0.625</v>
+        <v>0.7</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>

--- a/r/case2/outputs/results/CaseStudy_2_results.xlsx
+++ b/r/case2/outputs/results/CaseStudy_2_results.xlsx
@@ -768,7 +768,7 @@
         <v>14.6684309495277</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0375874561216122</v>
+        <v>0.0375874561216119</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
         <v>0.146126536878362</v>
       </c>
       <c r="D4" t="n">
-        <v>0.178186278495677</v>
+        <v>0.178186278495676</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -813,13 +813,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0755869199868573</v>
+        <v>0.0755869199868571</v>
       </c>
       <c r="C5" t="n">
         <v>0.0895276682326294</v>
       </c>
       <c r="D5" t="n">
-        <v>0.404085656410112</v>
+        <v>0.404085656410113</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -925,7 +925,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>-761.193300977685</v>
+        <v>-761.193300977686</v>
       </c>
       <c r="E4" t="n">
         <v>335</v>
@@ -977,7 +977,7 @@
         <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>-877.702938593218</v>
+        <v>-877.702938593219</v>
       </c>
       <c r="E6" t="n">
         <v>376</v>

--- a/r/case2/outputs/results/CaseStudy_2_results.xlsx
+++ b/r/case2/outputs/results/CaseStudy_2_results.xlsx
@@ -768,7 +768,7 @@
         <v>14.6684309495277</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0375874561216119</v>
+        <v>0.0375874561216122</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -802,7 +802,7 @@
         <v>0.146126536878362</v>
       </c>
       <c r="D4" t="n">
-        <v>0.178186278495676</v>
+        <v>0.178186278495677</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -813,13 +813,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0755869199868571</v>
+        <v>0.0755869199868573</v>
       </c>
       <c r="C5" t="n">
         <v>0.0895276682326294</v>
       </c>
       <c r="D5" t="n">
-        <v>0.404085656410113</v>
+        <v>0.404085656410112</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -925,7 +925,7 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>-761.193300977686</v>
+        <v>-761.193300977685</v>
       </c>
       <c r="E4" t="n">
         <v>335</v>
@@ -977,7 +977,7 @@
         <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>-877.702938593219</v>
+        <v>-877.702938593218</v>
       </c>
       <c r="E6" t="n">
         <v>376</v>
